--- a/data/trans_dic/P6907S1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 21,1</t>
+          <t>5,76; 20,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,1</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 18,81</t>
+          <t>2,13; 19,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 25,91</t>
+          <t>5,91; 26,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,77</t>
+          <t>0,0; 32,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,43</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 21,08</t>
+          <t>6,33; 20,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,83</t>
+          <t>6,99; 19,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,77</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 16,42</t>
+          <t>6,16; 16,71</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 35,02</t>
+          <t>7,01; 35,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,59</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,38</t>
+          <t>0,0; 18,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 21,5</t>
+          <t>3,33; 20,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,0</t>
+          <t>2,77; 23,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 33,13</t>
+          <t>5,72; 32,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 25,07</t>
+          <t>6,99; 24,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,45</t>
+          <t>0,0; 21,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,21</t>
+          <t>0,0; 9,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 23,9</t>
+          <t>6,3; 22,29</t>
         </is>
       </c>
     </row>
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 18,26</t>
+          <t>3,89; 17,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,73</t>
+          <t>2,85; 22,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 16,16</t>
+          <t>3,09; 16,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 40,71</t>
+          <t>13,59; 41,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,36</t>
+          <t>0,0; 26,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 31,64</t>
+          <t>2,64; 30,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 16,66</t>
+          <t>4,23; 16,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 15,88</t>
+          <t>2,6; 15,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 34,16</t>
+          <t>12,03; 33,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,35</t>
+          <t>3,34; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 16,96</t>
+          <t>1,87; 17,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,5</t>
+          <t>3,83; 13,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 26,38</t>
+          <t>7,12; 27,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,24</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,91</t>
+          <t>3,77; 13,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,52</t>
+          <t>4,73; 11,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,41</t>
+          <t>1,16; 11,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,39</t>
+          <t>0,42; 4,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,68</t>
+          <t>4,92; 12,06</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 20,96</t>
+          <t>4,18; 21,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,15</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 18,13</t>
+          <t>2,53; 19,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,77</t>
+          <t>3,03; 15,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,8</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,53</t>
+          <t>0,88; 6,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,63</t>
+          <t>4,63; 15,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,11</t>
+          <t>0,87; 8,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,56</t>
+          <t>1,71; 8,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,84; 12,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,6; 10,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,76; 5,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,76; 15,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,24; 16,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,86; 7,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,88; 5,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,33; 11,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,53; 12,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,25; 7,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,85; 5,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,75; 11,6</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>6,64; 12,13</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2,68; 9,72</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 6,03</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7,88; 15,11</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 15,58</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 7,73</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 5,44</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5,02; 10,95</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 12,22</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2,34; 7,57</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1,9; 4,76</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,94; 11,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene algún otro problema</t>
+          <t>Población que su trabajo le afecta de manera que tiene algún otro problema (tasa de respuesta: 88,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3635; 13730</t>
+          <t>3749; 13609</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1880</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6145</t>
+          <t>0; 4717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1074; 8620</t>
+          <t>974; 9048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2119; 12087</t>
+          <t>2757; 12307</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6086</t>
+          <t>0; 5770</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6170</t>
+          <t>0; 4941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3699; 12499</t>
+          <t>3752; 12216</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7682; 22162</t>
+          <t>7815; 22139</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 7554</t>
+          <t>0; 5988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6667</t>
+          <t>0; 6695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6165; 17257</t>
+          <t>6472; 17564</t>
         </is>
       </c>
     </row>
@@ -2135,27 +1994,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3045; 14832</t>
+          <t>2967; 15210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4464</t>
+          <t>0; 4596</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5556</t>
+          <t>0; 5656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1827; 10917</t>
+          <t>1693; 10523</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1177; 9987</t>
+          <t>1151; 9708</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2024,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1932</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2786; 13968</t>
+          <t>2412; 13668</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6355; 21048</t>
+          <t>5865; 20858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6835</t>
+          <t>0; 5873</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5494</t>
+          <t>0; 5713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5903; 22210</t>
+          <t>5855; 20718</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4757; 18263</t>
+          <t>3895; 17373</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>934; 8334</t>
+          <t>924; 7160</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2019; 10812</t>
+          <t>2065; 11066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8010; 23826</t>
+          <t>7954; 24189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1793</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>496; 5644</t>
+          <t>471; 5473</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5007; 19375</t>
+          <t>4926; 19195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>928; 7922</t>
+          <t>930; 7918</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2096; 12139</t>
+          <t>1987; 11870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9111; 26087</t>
+          <t>9187; 25707</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6677; 20787</t>
+          <t>6702; 21079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1031; 9067</t>
+          <t>1000; 9195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6643</t>
+          <t>0; 5711</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5722; 17980</t>
+          <t>5098; 17653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3220; 13177</t>
+          <t>3558; 13559</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6926</t>
+          <t>0; 6850</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3845; 14707</t>
+          <t>3984; 14512</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11947; 28888</t>
+          <t>11869; 29029</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1037; 9236</t>
+          <t>1026; 10050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>939; 9701</t>
+          <t>933; 10061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11475; 27916</t>
+          <t>11746; 28813</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2664; 13418</t>
+          <t>2677; 13813</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7011</t>
+          <t>0; 7180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1046; 9276</t>
+          <t>1293; 9755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1934; 11006</t>
+          <t>1986; 10441</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 8422</t>
+          <t>0; 7401</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1122; 8314</t>
+          <t>1121; 8248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5967; 20257</t>
+          <t>6006; 20426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1024; 10607</t>
+          <t>1007; 9927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3265; 15281</t>
+          <t>3050; 14640</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23625</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64223</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32292; 57892</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3708; 15108</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6155; 20359</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26360; 51777</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15931; 35361</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>865; 7292</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1914; 12838</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18770; 40044</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>52127; 84594</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5467; 18786</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10465; 29009</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46700; 80229</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>43508</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>7827</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12203</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>36776</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23625</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>27447</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>67134</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>10676</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>17538</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>64223</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>31374; 57283</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3828; 13864</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>6822; 21090</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>26759; 51294</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>16145; 34298</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>901; 7739</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1873; 11770</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>17678; 38585</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>52223; 84638</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>5690; 18377</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>10744; 26956</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>48028; 82907</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6907S1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6907S1-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 20,91</t>
+          <t>5,73; 20,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 19,75</t>
+          <t>2,43; 25,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 26,38</t>
+          <t>6,08; 25,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,97</t>
+          <t>0,0; 33,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,6</t>
+          <t>6,85; 21,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 19,81</t>
+          <t>7,34; 20,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 16,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,21</t>
+          <t>0,0; 7,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 16,71</t>
+          <t>6,83; 19,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 35,91</t>
+          <t>8,4; 35,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 23,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,71</t>
+          <t>0,0; 18,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 20,72</t>
+          <t>3,46; 21,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 23,33</t>
+          <t>2,45; 22,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,77</t>
+          <t>0,0; 64,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 32,42</t>
+          <t>5,81; 31,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 24,84</t>
+          <t>7,32; 23,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,87</t>
+          <t>0,0; 22,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 11,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 22,29</t>
+          <t>6,01; 20,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 17,37</t>
+          <t>4,38; 18,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 22,1</t>
+          <t>2,86; 23,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 16,54</t>
+          <t>3,16; 17,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,59; 41,33</t>
+          <t>13,36; 40,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,48</t>
+          <t>0,0; 25,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 30,68</t>
+          <t>2,34; 26,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 16,5</t>
+          <t>4,33; 16,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,02</t>
+          <t>1,77; 15,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,52</t>
+          <t>2,85; 15,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 33,67</t>
+          <t>11,93; 34,29</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,5</t>
+          <t>3,39; 10,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,2</t>
+          <t>1,91; 16,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 13,25</t>
+          <t>3,43; 11,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 27,15</t>
+          <t>5,98; 24,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,15</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 13,72</t>
+          <t>3,62; 13,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,58</t>
+          <t>4,81; 11,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,33</t>
+          <t>1,16; 10,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,55</t>
+          <t>0,42; 4,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,06</t>
+          <t>4,46; 10,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 21,58</t>
+          <t>4,15; 20,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 19,06</t>
+          <t>1,33; 16,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 15,91</t>
+          <t>2,82; 15,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,64</t>
+          <t>0,0; 16,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,48</t>
+          <t>2,27; 9,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 15,76</t>
+          <t>4,48; 15,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,53</t>
+          <t>0,87; 8,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,21</t>
+          <t>3,04; 9,72</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,26</t>
+          <t>6,61; 12,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 10,6</t>
+          <t>2,62; 10,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,82</t>
+          <t>1,74; 5,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,25</t>
+          <t>7,27; 14,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,06</t>
+          <t>7,03; 15,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,28</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,94</t>
+          <t>0,81; 5,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,37</t>
+          <t>6,23; 12,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,53; 12,22</t>
+          <t>7,72; 12,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,74</t>
+          <t>2,42; 7,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,12</t>
+          <t>1,91; 4,95</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,6</t>
+          <t>7,5; 12,51</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>13701</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3749; 13609</t>
+          <t>3728; 13660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1796,52 +1796,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 5580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>974; 9048</t>
+          <t>1263; 13504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2757; 12307</t>
+          <t>2837; 12041</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5770</t>
+          <t>0; 5854</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4941</t>
+          <t>0; 5918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3752; 12216</t>
+          <t>4249; 13189</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7815; 22139</t>
+          <t>8199; 22885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 6825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6695</t>
+          <t>0; 7005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6472; 17564</t>
+          <t>7794; 22108</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11517</t>
         </is>
       </c>
     </row>
@@ -1994,32 +1994,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2967; 15210</t>
+          <t>3559; 15162</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4596</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5656</t>
+          <t>0; 5552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1693; 10523</t>
+          <t>1802; 11220</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1151; 9708</t>
+          <t>1018; 9547</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4000</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2029,27 +2029,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2412; 13668</t>
+          <t>2640; 14341</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5865; 20858</t>
+          <t>6143; 19800</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5873</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 6849</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5855; 20718</t>
+          <t>5856; 20352</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>16578</t>
         </is>
       </c>
     </row>
@@ -2202,27 +2202,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3895; 17373</t>
+          <t>4382; 18015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>924; 7160</t>
+          <t>926; 7700</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2065; 11066</t>
+          <t>2114; 11960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7954; 24189</t>
+          <t>8216; 25201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4313</t>
+          <t>0; 4214</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2237,27 +2237,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>471; 5473</t>
+          <t>479; 5402</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4926; 19195</t>
+          <t>5041; 19199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930; 7918</t>
+          <t>934; 7995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1987; 11870</t>
+          <t>2178; 11755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9187; 25707</t>
+          <t>9774; 28094</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18700</t>
         </is>
       </c>
     </row>
@@ -2410,27 +2410,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6702; 21079</t>
+          <t>6807; 21413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1000; 9195</t>
+          <t>1019; 8739</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5711</t>
+          <t>0; 6509</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5098; 17653</t>
+          <t>5267; 18150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3558; 13559</t>
+          <t>2985; 12447</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6850</t>
+          <t>0; 6277</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3984; 14512</t>
+          <t>4122; 15527</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11869; 29029</t>
+          <t>12067; 29868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1026; 10050</t>
+          <t>1027; 9276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933; 10061</t>
+          <t>936; 8904</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11746; 28813</t>
+          <t>11937; 28571</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>9449</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2677; 13813</t>
+          <t>2658; 13282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7180</t>
+          <t>0; 6576</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1293; 9755</t>
+          <t>875; 10793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1986; 10441</t>
+          <t>1850; 10464</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2648,17 +2648,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7401</t>
+          <t>0; 7907</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1121; 8248</t>
+          <t>2305; 9821</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6006; 20426</t>
+          <t>5805; 19963</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1007; 9927</t>
+          <t>1016; 10034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3050; 14640</t>
+          <t>5090; 16261</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>39513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64223</t>
+          <t>69946</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32292; 57892</t>
+          <t>31212; 58423</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3708; 15108</t>
+          <t>3736; 14741</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6155; 20359</t>
+          <t>6088; 20082</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26360; 51777</t>
+          <t>27991; 56998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15931; 35361</t>
+          <t>15468; 33934</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>865; 7292</t>
+          <t>881; 7526</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1914; 12838</t>
+          <t>1754; 11305</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18770; 40044</t>
+          <t>21387; 41583</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52127; 84594</t>
+          <t>53477; 84837</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5467; 18786</t>
+          <t>5871; 19125</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10465; 29009</t>
+          <t>10833; 28057</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46700; 80229</t>
+          <t>54602; 91124</t>
         </is>
       </c>
     </row>
